--- a/AAII_Financials/Quarterly/OPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OPT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>OPT</t>
   </si>
@@ -656,67 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -736,19 +740,22 @@
         <v>100</v>
       </c>
       <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -759,28 +766,31 @@
         <v>100</v>
       </c>
       <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
         <v>200</v>
       </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
       <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -791,28 +801,31 @@
         <v>0</v>
       </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
         <v>-100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -825,40 +838,44 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E12" s="3">
         <v>60700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>61400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>78700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>25900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,8 +906,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -921,8 +941,11 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -953,8 +976,11 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -964,72 +990,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>93900</v>
+      </c>
+      <c r="E17" s="3">
         <v>71400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>79000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>96700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>39500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>39700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36900</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-93800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-71300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-78900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-96600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-39400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-39600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-17000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-36700</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1042,51 +1075,55 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E20" s="3">
         <v>12000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-90700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-59300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-75600</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>16</v>
@@ -1106,19 +1143,22 @@
       <c r="L21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E22" s="3">
         <v>10000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3500</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>16</v>
@@ -1138,72 +1178,81 @@
       <c r="L22" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-101200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-69300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-79100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-99100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-50300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-28300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-6300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-5700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-14600</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1234,72 +1283,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-96200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-65400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-77100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-92800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-37700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-45300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-96200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-65400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-77100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-92800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-37700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-45300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1330,8 +1388,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1362,8 +1423,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1394,8 +1458,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1426,72 +1493,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-12000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-96200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-65400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-77100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-92800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-37700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-45300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1522,77 +1598,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-96200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-65400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-77100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-92800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-37700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-45300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1605,8 +1690,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1619,40 +1705,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>157100</v>
+      </c>
+      <c r="E41" s="3">
         <v>89200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>141800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>44600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>88300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>118200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>202500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>42700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>75100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21500</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1683,40 +1773,46 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E43" s="3">
         <v>6600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1747,72 +1843,81 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E45" s="3">
         <v>2600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>17300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>300</v>
       </c>
       <c r="K45" s="3">
         <v>300</v>
       </c>
       <c r="L45" s="3">
+        <v>300</v>
+      </c>
+      <c r="M45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>166300</v>
+      </c>
+      <c r="E46" s="3">
         <v>98400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>153700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>59900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>109000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>138100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>213000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>49000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>79500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36900</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1825,8 +1930,8 @@
       <c r="F47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="G47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H47" s="3">
         <v>0</v>
@@ -1835,16 +1940,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
         <v>200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1855,28 +1963,31 @@
         <v>200</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
         <v>100</v>
       </c>
       <c r="I48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>200</v>
       </c>
       <c r="K48" s="3">
+        <v>200</v>
+      </c>
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1907,8 +2018,11 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1939,8 +2053,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1971,13 +2088,16 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
@@ -1989,22 +2109,25 @@
         <v>100</v>
       </c>
       <c r="H52" s="3">
+        <v>100</v>
+      </c>
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="J52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>16</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2035,40 +2158,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>166500</v>
+      </c>
+      <c r="E54" s="3">
         <v>98600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>154000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>60000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>109200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>138400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>213200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>49400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>80300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37700</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2081,8 +2210,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2095,40 +2225,44 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E57" s="3">
         <v>17800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2139,10 +2273,10 @@
         <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>100</v>
@@ -2156,11 +2290,14 @@
       <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="L58" s="3" t="s">
+      <c r="L58" s="3">
+        <v>100</v>
+      </c>
+      <c r="M58" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2168,75 +2305,81 @@
         <v>800</v>
       </c>
       <c r="E59" s="3">
+        <v>800</v>
+      </c>
+      <c r="F59" s="3">
         <v>700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>500</v>
       </c>
       <c r="H59" s="3">
         <v>500</v>
       </c>
       <c r="I59" s="3">
+        <v>500</v>
+      </c>
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E60" s="3">
         <v>18700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>180800</v>
+      </c>
+      <c r="E61" s="3">
         <v>85700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>88100</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -2244,19 +2387,22 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>100</v>
       </c>
       <c r="K61" s="3">
+        <v>100</v>
+      </c>
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2276,19 +2422,22 @@
         <v>0</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
       <c r="K62" s="3">
         <v>0</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2319,8 +2468,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2351,8 +2503,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2383,40 +2538,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>213400</v>
+      </c>
+      <c r="E66" s="3">
         <v>104500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>97500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2429,8 +2590,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2461,8 +2623,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2493,8 +2658,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2525,8 +2693,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2557,40 +2728,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-442400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-326700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-285300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-208500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-155500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-120000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-130900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-75700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-89400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-82600</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2621,8 +2798,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2653,8 +2833,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2685,40 +2868,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-5900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>56500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>48000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>100300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>135300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>197600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>73600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2749,77 +2938,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-96200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-65400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-77100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-92800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-37700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-45300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2832,8 +3030,9 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2864,8 +3063,11 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2896,8 +3098,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2928,8 +3133,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2960,8 +3168,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2992,8 +3203,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3024,40 +3238,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-69400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-51300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-69300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-71300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-28800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-45500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-18500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24200</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3070,8 +3290,9 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3102,8 +3323,11 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3134,8 +3358,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3166,8 +3393,11 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3184,22 +3414,25 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>900</v>
-      </c>
-      <c r="J94" s="3">
-        <v>500</v>
       </c>
       <c r="K94" s="3">
         <v>500</v>
       </c>
       <c r="L94" s="3">
+        <v>500</v>
+      </c>
+      <c r="M94" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3212,8 +3445,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3244,8 +3478,11 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3276,8 +3513,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3308,8 +3548,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3340,100 +3583,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>138400</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>167200</v>
-      </c>
-      <c r="F100" s="3">
-        <v>200</v>
       </c>
       <c r="G100" s="3">
         <v>200</v>
       </c>
       <c r="H100" s="3">
+        <v>200</v>
+      </c>
+      <c r="I100" s="3">
         <v>116900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>164800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>49000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>49100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>14400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-52600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>97100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-73600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-29900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>75500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>140500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>40500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>53600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>OPT</t>
   </si>
@@ -656,71 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -743,24 +747,27 @@
         <v>100</v>
       </c>
       <c r="J8" s="3">
+        <v>100</v>
+      </c>
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -769,33 +776,36 @@
         <v>100</v>
       </c>
       <c r="G9" s="3">
+        <v>100</v>
+      </c>
+      <c r="H9" s="3">
         <v>200</v>
       </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
       <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -804,28 +814,31 @@
         <v>0</v>
       </c>
       <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>-100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -839,43 +852,47 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E12" s="3">
         <v>84600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>60700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>61400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>78700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>31800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>25900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -909,8 +926,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,8 +964,11 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -979,8 +1002,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -991,78 +1017,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E17" s="3">
         <v>93900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>71400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>79000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>96700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>39500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>39700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36900</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-98100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-93800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-71300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-78900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-96600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-39400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-39600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-17000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-36700</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1076,57 +1109,61 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E20" s="3">
         <v>3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>12000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-10600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-108700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-90700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-59300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-75600</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>16</v>
@@ -1146,22 +1183,25 @@
       <c r="M21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E22" s="3">
         <v>10500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3500</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>16</v>
@@ -1181,78 +1221,87 @@
       <c r="M22" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-128400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-101200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-69300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-79100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-99100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-40600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-50300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-28300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-5000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-6300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-4900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-5700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-14600</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1286,78 +1335,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-124100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-96200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-65400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-77100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-92800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-37700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-45300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-124100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-96200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-65400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-77100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-92800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-37700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-45300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1391,8 +1449,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1426,8 +1487,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1461,8 +1525,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1496,78 +1563,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-12000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>10600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-124100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-96200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-65400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-77100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-92800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-37700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-45300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1601,83 +1677,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-124100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-96200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-65400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-77100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-92800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-37700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-45300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1691,8 +1776,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1706,43 +1792,47 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>172500</v>
+      </c>
+      <c r="E41" s="3">
         <v>157100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>89200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>141800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>44600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>88300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>118200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>202500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>42700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>75100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1776,43 +1866,49 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E43" s="3">
         <v>5800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1846,92 +1942,101 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E45" s="3">
         <v>3500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>17300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>300</v>
       </c>
       <c r="L45" s="3">
         <v>300</v>
       </c>
       <c r="M45" s="3">
+        <v>300</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>188200</v>
+      </c>
+      <c r="E46" s="3">
         <v>166300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>98400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>153700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>59900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>109000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>138100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>213000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>49000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>79500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>36900</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>16</v>
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
       </c>
       <c r="H47" s="3">
         <v>0</v>
@@ -1943,21 +2048,24 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
         <v>200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3">
         <v>200</v>
@@ -1966,28 +2074,31 @@
         <v>200</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
         <v>100</v>
       </c>
       <c r="J48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
       </c>
       <c r="L48" s="3">
+        <v>200</v>
+      </c>
+      <c r="M48" s="3">
         <v>400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2021,8 +2132,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2056,8 +2170,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2091,16 +2208,19 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -2112,22 +2232,25 @@
         <v>100</v>
       </c>
       <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="K52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>16</v>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2161,43 +2284,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>188800</v>
+      </c>
+      <c r="E54" s="3">
         <v>166500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>98600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>154000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>60000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>109200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>138400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>213200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>49400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>80300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>37700</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2211,8 +2340,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2226,43 +2356,47 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E57" s="3">
         <v>31700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2276,10 +2410,10 @@
         <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <v>100</v>
@@ -2293,96 +2427,105 @@
       <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="M58" s="3">
+        <v>100</v>
+      </c>
+      <c r="N58" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>800</v>
+        <v>25900</v>
       </c>
       <c r="E59" s="3">
         <v>800</v>
       </c>
       <c r="F59" s="3">
+        <v>800</v>
+      </c>
+      <c r="G59" s="3">
         <v>700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>500</v>
       </c>
       <c r="I59" s="3">
         <v>500</v>
       </c>
       <c r="J59" s="3">
+        <v>500</v>
+      </c>
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E60" s="3">
         <v>32600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200500</v>
+      </c>
+      <c r="E61" s="3">
         <v>180800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>85700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>88100</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2390,19 +2533,22 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>100</v>
       </c>
       <c r="L61" s="3">
+        <v>100</v>
+      </c>
+      <c r="M61" s="3">
         <v>200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2425,19 +2571,22 @@
         <v>0</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2471,8 +2620,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2506,8 +2658,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2541,43 +2696,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>264600</v>
+      </c>
+      <c r="E66" s="3">
         <v>213400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>104500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>97500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2591,8 +2752,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2626,8 +2788,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2661,8 +2826,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2696,8 +2864,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2731,43 +2902,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-563100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-442400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-326700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-285300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-208500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-155500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-120000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-130900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-75700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-89400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-82600</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2801,8 +2978,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2836,8 +3016,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2871,43 +3054,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-75800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-46900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-5900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>56500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>48000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>100300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>135300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>197600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>73600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2941,83 +3130,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-124100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-96200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-65400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-77100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-92800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-37700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-45300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3031,8 +3229,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3066,8 +3265,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3101,8 +3303,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3136,8 +3341,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3171,8 +3379,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3206,8 +3417,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3241,43 +3455,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-91700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-69400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-51300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-69300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-71300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-28800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-45500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-18500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-24200</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3291,8 +3511,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3326,8 +3547,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3361,8 +3585,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3396,8 +3623,11 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3417,22 +3647,25 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>900</v>
-      </c>
-      <c r="K94" s="3">
-        <v>500</v>
       </c>
       <c r="L94" s="3">
         <v>500</v>
       </c>
       <c r="M94" s="3">
+        <v>500</v>
+      </c>
+      <c r="N94" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3446,8 +3679,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3481,8 +3715,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3516,8 +3753,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3551,8 +3791,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3586,109 +3829,121 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>105300</v>
+      </c>
+      <c r="E100" s="3">
         <v>138400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>167200</v>
-      </c>
-      <c r="G100" s="3">
-        <v>200</v>
       </c>
       <c r="H100" s="3">
         <v>200</v>
       </c>
       <c r="I100" s="3">
+        <v>200</v>
+      </c>
+      <c r="J100" s="3">
         <v>116900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>164800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>49000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>49100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>14400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E102" s="3">
         <v>67900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-52600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>97100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-73600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-29900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>75500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>140500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>40500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>53600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>OPT</t>
   </si>
@@ -663,13 +663,11 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -694,22 +692,22 @@
         <v>45473</v>
       </c>
       <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44377</v>
       </c>
       <c r="K7" s="2">
         <v>44196</v>
@@ -728,11 +726,11 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>100</v>
+      <c r="D8" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
@@ -770,7 +768,7 @@
         <v>-100</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F9" s="3">
         <v>100</v>
@@ -779,13 +777,13 @@
         <v>100</v>
       </c>
       <c r="H9" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
       </c>
       <c r="J9" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3">
         <v>100</v>
@@ -805,10 +803,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -817,13 +815,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3">
         <v>100</v>
       </c>
       <c r="J10" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3">
         <v>100</v>
@@ -859,25 +857,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>91700</v>
+        <v>45700</v>
       </c>
       <c r="E12" s="3">
-        <v>84600</v>
+        <v>45700</v>
       </c>
       <c r="F12" s="3">
-        <v>60700</v>
+        <v>42300</v>
       </c>
       <c r="G12" s="3">
-        <v>61400</v>
+        <v>42300</v>
       </c>
       <c r="H12" s="3">
-        <v>78700</v>
+        <v>33600</v>
       </c>
       <c r="I12" s="3">
-        <v>31800</v>
+        <v>33600</v>
       </c>
       <c r="J12" s="3">
-        <v>25900</v>
+        <v>30700</v>
       </c>
       <c r="K12" s="3">
         <v>13800</v>
@@ -934,26 +932,26 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1024,25 +1022,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>98200</v>
+        <v>49100</v>
       </c>
       <c r="E17" s="3">
-        <v>93900</v>
+        <v>49100</v>
       </c>
       <c r="F17" s="3">
-        <v>71400</v>
+        <v>47000</v>
       </c>
       <c r="G17" s="3">
-        <v>79000</v>
+        <v>47000</v>
       </c>
       <c r="H17" s="3">
-        <v>96700</v>
+        <v>35700</v>
       </c>
       <c r="I17" s="3">
+        <v>35700</v>
+      </c>
+      <c r="J17" s="3">
         <v>39500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>39700</v>
       </c>
       <c r="K17" s="3">
         <v>19300</v>
@@ -1062,25 +1060,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-98100</v>
+        <v>-49100</v>
       </c>
       <c r="E18" s="3">
-        <v>-93800</v>
+        <v>-49100</v>
       </c>
       <c r="F18" s="3">
-        <v>-71300</v>
+        <v>-46900</v>
       </c>
       <c r="G18" s="3">
-        <v>-78900</v>
+        <v>-46900</v>
       </c>
       <c r="H18" s="3">
-        <v>-96600</v>
+        <v>-35600</v>
       </c>
       <c r="I18" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="J18" s="3">
         <v>-39400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-39600</v>
       </c>
       <c r="K18" s="3">
         <v>-19100</v>
@@ -1116,25 +1114,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-10600</v>
+        <v>6100</v>
       </c>
       <c r="E20" s="3">
-        <v>3100</v>
+        <v>6100</v>
       </c>
       <c r="F20" s="3">
-        <v>12000</v>
+        <v>-600</v>
       </c>
       <c r="G20" s="3">
-        <v>3200</v>
+        <v>-600</v>
       </c>
       <c r="H20" s="3">
-        <v>-2500</v>
+        <v>-4900</v>
       </c>
       <c r="I20" s="3">
-        <v>-1200</v>
+        <v>-4900</v>
       </c>
       <c r="J20" s="3">
-        <v>-10600</v>
+        <v>-1000</v>
       </c>
       <c r="K20" s="3">
         <v>-9200</v>
@@ -1154,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-108700</v>
+        <v>-55100</v>
       </c>
       <c r="E21" s="3">
-        <v>-90700</v>
+        <v>-55100</v>
       </c>
       <c r="F21" s="3">
-        <v>-59300</v>
+        <v>-46300</v>
       </c>
       <c r="G21" s="3">
-        <v>-75600</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>16</v>
+        <v>-46300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-38400</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>16</v>
@@ -1192,25 +1190,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>19800</v>
+        <v>9900</v>
       </c>
       <c r="E22" s="3">
-        <v>10500</v>
+        <v>9900</v>
       </c>
       <c r="F22" s="3">
-        <v>10000</v>
+        <v>5200</v>
       </c>
       <c r="G22" s="3">
-        <v>3500</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>16</v>
+        <v>5200</v>
+      </c>
+      <c r="H22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1700</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>16</v>
@@ -1230,25 +1228,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-128400</v>
+        <v>-64200</v>
       </c>
       <c r="E23" s="3">
-        <v>-101200</v>
+        <v>-64200</v>
       </c>
       <c r="F23" s="3">
-        <v>-69300</v>
+        <v>-50600</v>
       </c>
       <c r="G23" s="3">
-        <v>-79100</v>
+        <v>-50600</v>
       </c>
       <c r="H23" s="3">
-        <v>-99100</v>
+        <v>-34700</v>
       </c>
       <c r="I23" s="3">
-        <v>-40600</v>
+        <v>-34700</v>
       </c>
       <c r="J23" s="3">
-        <v>-50300</v>
+        <v>-39600</v>
       </c>
       <c r="K23" s="3">
         <v>-28300</v>
@@ -1268,25 +1266,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-4400</v>
+        <v>-2200</v>
       </c>
       <c r="E24" s="3">
-        <v>-5000</v>
+        <v>-2200</v>
       </c>
       <c r="F24" s="3">
-        <v>-3900</v>
+        <v>-2500</v>
       </c>
       <c r="G24" s="3">
-        <v>-2000</v>
+        <v>-2500</v>
       </c>
       <c r="H24" s="3">
-        <v>-6300</v>
+        <v>-1900</v>
       </c>
       <c r="I24" s="3">
-        <v>-2900</v>
+        <v>-1900</v>
       </c>
       <c r="J24" s="3">
-        <v>-4900</v>
+        <v>-1000</v>
       </c>
       <c r="K24" s="3">
         <v>-2500</v>
@@ -1344,25 +1342,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-124100</v>
+        <v>-62000</v>
       </c>
       <c r="E26" s="3">
-        <v>-96200</v>
+        <v>-62000</v>
       </c>
       <c r="F26" s="3">
-        <v>-65400</v>
+        <v>-48100</v>
       </c>
       <c r="G26" s="3">
-        <v>-77100</v>
+        <v>-48100</v>
       </c>
       <c r="H26" s="3">
-        <v>-92800</v>
+        <v>-32700</v>
       </c>
       <c r="I26" s="3">
-        <v>-37700</v>
+        <v>-32700</v>
       </c>
       <c r="J26" s="3">
-        <v>-45300</v>
+        <v>-38500</v>
       </c>
       <c r="K26" s="3">
         <v>-25700</v>
@@ -1382,25 +1380,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-124100</v>
+        <v>-62000</v>
       </c>
       <c r="E27" s="3">
-        <v>-96200</v>
+        <v>-62000</v>
       </c>
       <c r="F27" s="3">
-        <v>-65400</v>
+        <v>-48100</v>
       </c>
       <c r="G27" s="3">
-        <v>-77100</v>
+        <v>-48100</v>
       </c>
       <c r="H27" s="3">
-        <v>-92800</v>
+        <v>-32700</v>
       </c>
       <c r="I27" s="3">
-        <v>-37700</v>
+        <v>-32700</v>
       </c>
       <c r="J27" s="3">
-        <v>-45300</v>
+        <v>-38500</v>
       </c>
       <c r="K27" s="3">
         <v>-25700</v>
@@ -1572,25 +1570,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>10600</v>
+        <v>-6100</v>
       </c>
       <c r="E32" s="3">
-        <v>-3100</v>
+        <v>-6100</v>
       </c>
       <c r="F32" s="3">
-        <v>-12000</v>
+        <v>600</v>
       </c>
       <c r="G32" s="3">
-        <v>-3200</v>
+        <v>600</v>
       </c>
       <c r="H32" s="3">
-        <v>2500</v>
+        <v>4900</v>
       </c>
       <c r="I32" s="3">
-        <v>1200</v>
+        <v>4900</v>
       </c>
       <c r="J32" s="3">
-        <v>10600</v>
+        <v>1000</v>
       </c>
       <c r="K32" s="3">
         <v>9200</v>
@@ -1610,25 +1608,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-124100</v>
+        <v>-62000</v>
       </c>
       <c r="E33" s="3">
-        <v>-96200</v>
+        <v>-62000</v>
       </c>
       <c r="F33" s="3">
-        <v>-65400</v>
+        <v>-48100</v>
       </c>
       <c r="G33" s="3">
-        <v>-77100</v>
+        <v>-48100</v>
       </c>
       <c r="H33" s="3">
-        <v>-92800</v>
+        <v>-32700</v>
       </c>
       <c r="I33" s="3">
-        <v>-37700</v>
+        <v>-32700</v>
       </c>
       <c r="J33" s="3">
-        <v>-45300</v>
+        <v>-38500</v>
       </c>
       <c r="K33" s="3">
         <v>-25700</v>
@@ -1686,25 +1684,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-124100</v>
+        <v>-62000</v>
       </c>
       <c r="E35" s="3">
-        <v>-96200</v>
+        <v>-62000</v>
       </c>
       <c r="F35" s="3">
-        <v>-65400</v>
+        <v>-48100</v>
       </c>
       <c r="G35" s="3">
-        <v>-77100</v>
+        <v>-48100</v>
       </c>
       <c r="H35" s="3">
-        <v>-92800</v>
+        <v>-32700</v>
       </c>
       <c r="I35" s="3">
-        <v>-37700</v>
+        <v>-32700</v>
       </c>
       <c r="J35" s="3">
-        <v>-45300</v>
+        <v>-38500</v>
       </c>
       <c r="K35" s="3">
         <v>-25700</v>
@@ -1732,22 +1730,22 @@
         <v>45473</v>
       </c>
       <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44377</v>
       </c>
       <c r="K38" s="2">
         <v>44196</v>
@@ -1802,22 +1800,22 @@
         <v>172500</v>
       </c>
       <c r="E41" s="3">
+        <v>172500</v>
+      </c>
+      <c r="F41" s="3">
         <v>157100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>157100</v>
+      </c>
+      <c r="H41" s="3">
         <v>89200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>89200</v>
+      </c>
+      <c r="J41" s="3">
         <v>141800</v>
-      </c>
-      <c r="H41" s="3">
-        <v>44600</v>
-      </c>
-      <c r="I41" s="3">
-        <v>88300</v>
-      </c>
-      <c r="J41" s="3">
-        <v>118200</v>
       </c>
       <c r="K41" s="3">
         <v>202500</v>
@@ -1878,22 +1876,22 @@
         <v>11800</v>
       </c>
       <c r="E43" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F43" s="3">
         <v>5800</v>
       </c>
-      <c r="F43" s="3">
-        <v>6600</v>
-      </c>
       <c r="G43" s="3">
-        <v>9200</v>
+        <v>5800</v>
       </c>
       <c r="H43" s="3">
         <v>6600</v>
       </c>
       <c r="I43" s="3">
-        <v>3400</v>
+        <v>6600</v>
       </c>
       <c r="J43" s="3">
-        <v>5500</v>
+        <v>9200</v>
       </c>
       <c r="K43" s="3">
         <v>4400</v>
@@ -1912,26 +1910,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1950,26 +1948,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>3900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>8700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>17300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>14400</v>
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K45" s="3">
         <v>6100</v>
@@ -1992,22 +1990,22 @@
         <v>188200</v>
       </c>
       <c r="E46" s="3">
+        <v>188200</v>
+      </c>
+      <c r="F46" s="3">
         <v>166300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>166300</v>
+      </c>
+      <c r="H46" s="3">
         <v>98400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>98400</v>
+      </c>
+      <c r="J46" s="3">
         <v>153700</v>
-      </c>
-      <c r="H46" s="3">
-        <v>59900</v>
-      </c>
-      <c r="I46" s="3">
-        <v>109000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>138100</v>
       </c>
       <c r="K46" s="3">
         <v>213000</v>
@@ -2026,26 +2024,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2068,7 +2066,7 @@
         <v>100</v>
       </c>
       <c r="E48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F48" s="3">
         <v>200</v>
@@ -2077,13 +2075,13 @@
         <v>200</v>
       </c>
       <c r="H48" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K48" s="3">
         <v>200</v>
@@ -2220,13 +2218,13 @@
         <v>500</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -2235,7 +2233,7 @@
         <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>16</v>
@@ -2296,22 +2294,22 @@
         <v>188800</v>
       </c>
       <c r="E54" s="3">
+        <v>188800</v>
+      </c>
+      <c r="F54" s="3">
         <v>166500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>166500</v>
+      </c>
+      <c r="H54" s="3">
         <v>98600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>98600</v>
+      </c>
+      <c r="J54" s="3">
         <v>154000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>60000</v>
-      </c>
-      <c r="I54" s="3">
-        <v>109200</v>
-      </c>
-      <c r="J54" s="3">
-        <v>138400</v>
       </c>
       <c r="K54" s="3">
         <v>213200</v>
@@ -2362,26 +2360,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>38100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>31700</v>
-      </c>
-      <c r="F57" s="3">
-        <v>17800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>8700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>11400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>8300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>2500</v>
+      <c r="D57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K57" s="3">
         <v>14700</v>
@@ -2413,7 +2411,7 @@
         <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
         <v>100</v>
@@ -2439,25 +2437,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25900</v>
+        <v>62900</v>
       </c>
       <c r="E59" s="3">
-        <v>800</v>
+        <v>62900</v>
       </c>
       <c r="F59" s="3">
-        <v>800</v>
+        <v>31700</v>
       </c>
       <c r="G59" s="3">
-        <v>700</v>
+        <v>31700</v>
       </c>
       <c r="H59" s="3">
-        <v>600</v>
+        <v>17800</v>
       </c>
       <c r="I59" s="3">
-        <v>500</v>
+        <v>17800</v>
       </c>
       <c r="J59" s="3">
-        <v>500</v>
+        <v>8700</v>
       </c>
       <c r="K59" s="3">
         <v>700</v>
@@ -2480,22 +2478,22 @@
         <v>64100</v>
       </c>
       <c r="E60" s="3">
+        <v>64100</v>
+      </c>
+      <c r="F60" s="3">
         <v>32600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>32600</v>
+      </c>
+      <c r="H60" s="3">
         <v>18700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>18700</v>
+      </c>
+      <c r="J60" s="3">
         <v>9400</v>
-      </c>
-      <c r="H60" s="3">
-        <v>12000</v>
-      </c>
-      <c r="I60" s="3">
-        <v>8900</v>
-      </c>
-      <c r="J60" s="3">
-        <v>3100</v>
       </c>
       <c r="K60" s="3">
         <v>15500</v>
@@ -2518,22 +2516,22 @@
         <v>200500</v>
       </c>
       <c r="E61" s="3">
+        <v>200500</v>
+      </c>
+      <c r="F61" s="3">
         <v>180800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>180800</v>
+      </c>
+      <c r="H61" s="3">
         <v>85700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
+        <v>85700</v>
+      </c>
+      <c r="J61" s="3">
         <v>88100</v>
-      </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>100</v>
@@ -2708,22 +2706,22 @@
         <v>264600</v>
       </c>
       <c r="E66" s="3">
+        <v>264600</v>
+      </c>
+      <c r="F66" s="3">
         <v>213400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
+        <v>213400</v>
+      </c>
+      <c r="H66" s="3">
         <v>104500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
+        <v>104500</v>
+      </c>
+      <c r="J66" s="3">
         <v>97500</v>
-      </c>
-      <c r="H66" s="3">
-        <v>12100</v>
-      </c>
-      <c r="I66" s="3">
-        <v>8900</v>
-      </c>
-      <c r="J66" s="3">
-        <v>3100</v>
       </c>
       <c r="K66" s="3">
         <v>15600</v>
@@ -2911,25 +2909,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-563100</v>
+        <v>-579700</v>
       </c>
       <c r="E72" s="3">
-        <v>-442400</v>
+        <v>-579700</v>
       </c>
       <c r="F72" s="3">
-        <v>-326700</v>
+        <v>-455600</v>
       </c>
       <c r="G72" s="3">
-        <v>-285300</v>
+        <v>-455600</v>
       </c>
       <c r="H72" s="3">
-        <v>-208500</v>
+        <v>-359500</v>
       </c>
       <c r="I72" s="3">
-        <v>-155500</v>
+        <v>-359500</v>
       </c>
       <c r="J72" s="3">
-        <v>-120000</v>
+        <v>-294000</v>
       </c>
       <c r="K72" s="3">
         <v>-130900</v>
@@ -3066,22 +3064,22 @@
         <v>-75800</v>
       </c>
       <c r="E76" s="3">
+        <v>-75800</v>
+      </c>
+      <c r="F76" s="3">
         <v>-46900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="H76" s="3">
         <v>-5900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J76" s="3">
         <v>56500</v>
-      </c>
-      <c r="H76" s="3">
-        <v>48000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>100300</v>
-      </c>
-      <c r="J76" s="3">
-        <v>135300</v>
       </c>
       <c r="K76" s="3">
         <v>197600</v>
@@ -3147,22 +3145,22 @@
         <v>45473</v>
       </c>
       <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44377</v>
       </c>
       <c r="K80" s="2">
         <v>44196</v>
@@ -3182,25 +3180,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-124100</v>
+        <v>-62000</v>
       </c>
       <c r="E81" s="3">
-        <v>-96200</v>
+        <v>-62000</v>
       </c>
       <c r="F81" s="3">
-        <v>-65400</v>
+        <v>-48100</v>
       </c>
       <c r="G81" s="3">
-        <v>-77100</v>
+        <v>-48100</v>
       </c>
       <c r="H81" s="3">
-        <v>-92800</v>
+        <v>-32700</v>
       </c>
       <c r="I81" s="3">
-        <v>-37700</v>
+        <v>-32700</v>
       </c>
       <c r="J81" s="3">
-        <v>-45300</v>
+        <v>-38500</v>
       </c>
       <c r="K81" s="3">
         <v>-25700</v>
@@ -3464,25 +3462,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-91700</v>
+        <v>-45800</v>
       </c>
       <c r="E89" s="3">
-        <v>-69400</v>
+        <v>-45800</v>
       </c>
       <c r="F89" s="3">
-        <v>-51300</v>
+        <v>-34700</v>
       </c>
       <c r="G89" s="3">
-        <v>-69300</v>
+        <v>-34700</v>
       </c>
       <c r="H89" s="3">
-        <v>-71300</v>
+        <v>-25700</v>
       </c>
       <c r="I89" s="3">
-        <v>-28800</v>
+        <v>-25700</v>
       </c>
       <c r="J89" s="3">
-        <v>-45500</v>
+        <v>-34600</v>
       </c>
       <c r="K89" s="3">
         <v>-18500</v>
@@ -3650,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="K94" s="3">
         <v>900</v>
@@ -3685,26 +3683,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3838,25 +3836,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>105300</v>
+        <v>52700</v>
       </c>
       <c r="E100" s="3">
-        <v>138400</v>
+        <v>52700</v>
       </c>
       <c r="F100" s="3">
-        <v>100</v>
+        <v>69200</v>
       </c>
       <c r="G100" s="3">
-        <v>167200</v>
+        <v>69200</v>
       </c>
       <c r="H100" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I100" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3">
-        <v>116900</v>
+        <v>83600</v>
       </c>
       <c r="K100" s="3">
         <v>164800</v>
@@ -3876,25 +3874,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>1700</v>
+        <v>-700</v>
       </c>
       <c r="E101" s="3">
-        <v>-1100</v>
+        <v>-700</v>
       </c>
       <c r="F101" s="3">
-        <v>-1300</v>
+        <v>-400</v>
       </c>
       <c r="G101" s="3">
-        <v>-800</v>
+        <v>-400</v>
       </c>
       <c r="H101" s="3">
-        <v>-2400</v>
+        <v>-500</v>
       </c>
       <c r="I101" s="3">
-        <v>-1400</v>
+        <v>-500</v>
       </c>
       <c r="J101" s="3">
-        <v>3500</v>
+        <v>-700</v>
       </c>
       <c r="K101" s="3">
         <v>14400</v>
@@ -3914,25 +3912,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>15400</v>
+        <v>7700</v>
       </c>
       <c r="E102" s="3">
-        <v>67900</v>
+        <v>7700</v>
       </c>
       <c r="F102" s="3">
-        <v>-52600</v>
+        <v>33900</v>
       </c>
       <c r="G102" s="3">
-        <v>97100</v>
+        <v>33900</v>
       </c>
       <c r="H102" s="3">
-        <v>-73600</v>
+        <v>-26300</v>
       </c>
       <c r="I102" s="3">
-        <v>-29900</v>
+        <v>-26300</v>
       </c>
       <c r="J102" s="3">
-        <v>75500</v>
+        <v>48600</v>
       </c>
       <c r="K102" s="3">
         <v>140500</v>

--- a/AAII_Financials/Quarterly/OPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>OPT</t>
   </si>
@@ -656,73 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45656</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -730,13 +737,13 @@
         <v>16</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <v>100</v>
@@ -748,57 +755,69 @@
         <v>100</v>
       </c>
       <c r="K8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L8" s="3">
         <v>100</v>
       </c>
       <c r="M8" s="3">
+        <v>200</v>
+      </c>
+      <c r="N8" s="3">
+        <v>100</v>
+      </c>
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="3">
         <v>-100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>-100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3">
-        <v>100</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3">
-        <v>100</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -809,10 +828,10 @@
         <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
@@ -827,16 +846,22 @@
         <v>100</v>
       </c>
       <c r="L10" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="M10" s="3">
         <v>100</v>
       </c>
       <c r="N10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O10" s="3">
+        <v>100</v>
+      </c>
+      <c r="P10" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -851,46 +876,54 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>34900</v>
+      </c>
+      <c r="F12" s="3">
         <v>45700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>45700</v>
       </c>
-      <c r="F12" s="3">
-        <v>42300</v>
-      </c>
-      <c r="G12" s="3">
-        <v>42300</v>
-      </c>
       <c r="H12" s="3">
+        <v>43600</v>
+      </c>
+      <c r="I12" s="3">
+        <v>43600</v>
+      </c>
+      <c r="J12" s="3">
         <v>33600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>33600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>30700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>13800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>12100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>8300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -927,8 +960,14 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -953,11 +992,11 @@
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -965,8 +1004,14 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1003,8 +1048,14 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,84 +1067,98 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>42600</v>
+      </c>
+      <c r="F17" s="3">
         <v>49100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>49100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>47000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>47000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>35700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>35700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>39500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>19300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>17100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>11900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>36900</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-49100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-49100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-46900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-46900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-35600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-35600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-39400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-19100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-17000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-11600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-36700</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1108,198 +1173,230 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>17200</v>
+      </c>
+      <c r="F20" s="3">
         <v>6100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>6100</v>
       </c>
-      <c r="F20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-600</v>
-      </c>
       <c r="H20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J20" s="3">
         <v>-4900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-4900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-9200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-59800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-59800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-55100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-55100</v>
       </c>
-      <c r="F21" s="3">
-        <v>-46300</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-46300</v>
-      </c>
       <c r="H21" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="J21" s="3">
         <v>-30700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-30700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-38400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F22" s="3">
         <v>9900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>9900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>5200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>5200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>5000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>5000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>1700</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-64200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-64200</v>
       </c>
-      <c r="F23" s="3">
-        <v>-50600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-50600</v>
-      </c>
       <c r="H23" s="3">
+        <v>-53400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-53400</v>
+      </c>
+      <c r="J23" s="3">
         <v>-34700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-34700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-39600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-28300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-16800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-11500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F24" s="3">
         <v>-2200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-2200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-2500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-2500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-2500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-5700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-3800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-14600</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1433,102 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-62000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-62000</v>
       </c>
-      <c r="F26" s="3">
-        <v>-48100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-48100</v>
-      </c>
       <c r="H26" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="J26" s="3">
         <v>-32700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-32700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-38500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-25700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-11100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-7600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-62000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-62000</v>
       </c>
-      <c r="F27" s="3">
-        <v>-48100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-48100</v>
-      </c>
       <c r="H27" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="J27" s="3">
         <v>-32700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-32700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-38500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-25700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-11100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-7600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1565,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1609,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1653,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,84 +1697,102 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-6100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-6100</v>
       </c>
-      <c r="F32" s="3">
-        <v>600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>600</v>
-      </c>
       <c r="H32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J32" s="3">
         <v>4900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>4900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>9200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-62000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-62000</v>
       </c>
-      <c r="F33" s="3">
-        <v>-48100</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-48100</v>
-      </c>
       <c r="H33" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="J33" s="3">
         <v>-32700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-32700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-38500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-25700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-11100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-7600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1829,107 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-62000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-62000</v>
       </c>
-      <c r="F35" s="3">
-        <v>-48100</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-48100</v>
-      </c>
       <c r="H35" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="J35" s="3">
         <v>-32700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-32700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-38500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-25700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-11100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-7600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45656</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1944,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,46 +1962,54 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>131900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>131900</v>
+      </c>
+      <c r="F41" s="3">
         <v>172500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>172500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>157100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>157100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>89200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>89200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>141800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>202500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>42700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>75100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>21500</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1867,46 +2046,58 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F43" s="3">
         <v>11800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>11800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>6600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>6600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>9200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>6100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1931,11 +2122,11 @@
       <c r="J44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -1943,8 +2134,14 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1969,58 +2166,70 @@
       <c r="J45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M45" s="3">
         <v>6100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>144100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>144100</v>
+      </c>
+      <c r="F46" s="3">
         <v>188200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>188200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>166300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>166300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>98400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>98400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>153700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>213000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>49000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>79500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>36900</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2045,34 +2254,40 @@
       <c r="J47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3">
         <v>100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>200</v>
       </c>
       <c r="H48" s="3">
         <v>200</v>
@@ -2090,13 +2305,19 @@
         <v>200</v>
       </c>
       <c r="M48" s="3">
+        <v>200</v>
+      </c>
+      <c r="N48" s="3">
+        <v>200</v>
+      </c>
+      <c r="O48" s="3">
         <v>400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2133,8 +2354,14 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2398,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,46 +2442,58 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F52" s="3">
         <v>500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>500</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>16</v>
+      <c r="K52" s="3">
+        <v>100</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2530,58 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>145800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>145800</v>
+      </c>
+      <c r="F54" s="3">
         <v>188800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>188800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>166500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>166500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>98600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>98600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>154000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>213200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>49400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>80300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>37700</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2596,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,8 +2614,10 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2381,28 +2642,34 @@
       <c r="J57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M57" s="3">
         <v>14700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>100</v>
@@ -2428,125 +2695,149 @@
       <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>100</v>
+      </c>
+      <c r="O58" s="3">
+        <v>100</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>65900</v>
+      </c>
+      <c r="F59" s="3">
         <v>62900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>62900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>31700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>31700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>17800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>17800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>8700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>91700</v>
+      </c>
+      <c r="F60" s="3">
         <v>64100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>64100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>32600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>32600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>18700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>18700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>9400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>15500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>222700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>222700</v>
+      </c>
+      <c r="F61" s="3">
         <v>200500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>200500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>180800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>180800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>85700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>85700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>88100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2572,19 +2863,25 @@
         <v>0</v>
       </c>
       <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2918,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2962,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +3006,58 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>314500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>314500</v>
+      </c>
+      <c r="F66" s="3">
         <v>264600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>264600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>213400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>213400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>104500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>104500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>97500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>15600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +3072,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +3112,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +3156,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3200,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3244,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-711600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-711600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-579700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-579700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-455600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-455600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-359500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-359500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-294000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-130900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-75700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-89400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-82600</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3332,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3376,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3420,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-168700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-168700</v>
+      </c>
+      <c r="F76" s="3">
         <v>-75800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-75800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-46900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-46900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-5900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-5900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>56500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>197600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>44600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>73600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3508,107 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45656</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-62000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-62000</v>
       </c>
-      <c r="F81" s="3">
-        <v>-48100</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-48100</v>
-      </c>
       <c r="H81" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="J81" s="3">
         <v>-32700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-32700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-38500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-25700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-11100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-7600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,16 +3623,18 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -3266,8 +3663,14 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3707,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3751,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3795,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3839,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3883,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-45800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-45800</v>
       </c>
-      <c r="F89" s="3">
-        <v>-34700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-34700</v>
-      </c>
       <c r="H89" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="J89" s="3">
         <v>-25700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-25700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-34600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-18500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-5700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>3900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-24200</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,8 +3949,10 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3548,8 +3989,14 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +4033,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,8 +4077,14 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3651,19 +4110,25 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,8 +4143,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3704,11 +4171,11 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -3716,8 +4183,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +4227,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4271,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,118 +4315,142 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>69200</v>
+      </c>
+      <c r="F100" s="3">
         <v>52700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>52700</v>
       </c>
-      <c r="F100" s="3">
-        <v>69200</v>
-      </c>
-      <c r="G100" s="3">
-        <v>69200</v>
-      </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>17400</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>17400</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>83600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>164800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>49000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>49100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>14400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>33900</v>
+      </c>
+      <c r="F102" s="3">
         <v>7700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>7700</v>
       </c>
-      <c r="F102" s="3">
-        <v>33900</v>
-      </c>
-      <c r="G102" s="3">
-        <v>33900</v>
-      </c>
       <c r="H102" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="J102" s="3">
         <v>-26300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-26300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>48600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>140500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>40500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>53600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-11000</v>
       </c>
     </row>
